--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-radiology.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-radiology.xlsx
@@ -4757,7 +4757,7 @@
         <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>81</v>
@@ -6129,7 +6129,7 @@
         <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-radiology.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-radiology.xlsx
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -379,7 +379,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -525,7 +525,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ImmunizationRecommendation|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -616,7 +616,7 @@
     <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -846,7 +846,7 @@
     <t>レポートを作成した臨床分野・部門、または診断サービス（CT, US, MRIなど）を分類するコード。 これは、検索、並べ替え、および表示の目的で使用される。【JP-Core仕様】放射線レポートは第1コードとして LP29684-5 を固定値として設定。第2コード以下にDICOMModalityコードを列挙することでレポートの対象検査内容を示す。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS|1.1.0</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.id</t>
@@ -900,7 +900,7 @@
     <t>レポート対象のモダリティを示すコード。放射線を表す第1コードのLP29684-5に続くサブカテゴリコードとして第2コード以下に保持される。複数のモダリティの組み合わせを許容するため、コードの列挙を許容する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>DiagnosticReport.category:second.id</t>
@@ -961,7 +961,7 @@
     <t>【JP Core仕様】[画像診断レポート交換手順ガイドライン](https://www.jira-net.or.jp/publishing/files/jesra/JESRA_TR-0042_2018.pdf)「5.1 レポート種別コード」に記載されているLOINCコード [Diagnostic imaging study](https://loinc.org/18748-4/) を指定。コードを指定できない場合はCodeableConceptを使用せずテキスト等を直接コーディングすることも許容されるが、要素間の調整と事前・事後の内容の整合性確保のために独自の構造を提供する必要があるので留意すること。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS|1.1.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1083,7 +1083,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Group|Device|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Group|4.0.1|Device|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1119,7 +1119,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1225,7 +1225,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1278,7 +1278,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1306,7 +1306,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Radiology_Findings|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Radiology_Impression|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Radiology_Findings|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Radiology_Impression|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1332,7 +1332,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ImagingStudy_Radiology)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ImagingStudy_Radiology|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1421,7 +1421,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media)
+    <t xml:space="preserve">Reference(Media|4.0.1)
 </t>
   </si>
   <si>
@@ -1481,7 +1481,7 @@
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
@@ -1839,7 +1839,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="190.17578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="214.1484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1854,7 +1854,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="62.875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-radiology.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-radiology.xlsx
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -379,7 +379,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -525,7 +525,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|ImmunizationRecommendation|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -616,7 +616,7 @@
     <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -846,7 +846,7 @@
     <t>レポートを作成した臨床分野・部門、または診断サービス（CT, US, MRIなど）を分類するコード。 これは、検索、並べ替え、および表示の目的で使用される。【JP-Core仕様】放射線レポートは第1コードとして LP29684-5 を固定値として設定。第2コード以下にDICOMModalityコードを列挙することでレポートの対象検査内容を示す。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.id</t>
@@ -900,7 +900,7 @@
     <t>レポート対象のモダリティを示すコード。放射線を表す第1コードのLP29684-5に続くサブカテゴリコードとして第2コード以下に保持される。複数のモダリティの組み合わせを許容するため、コードの列挙を許容する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
   </si>
   <si>
     <t>DiagnosticReport.category:second.id</t>
@@ -961,7 +961,7 @@
     <t>【JP Core仕様】[画像診断レポート交換手順ガイドライン](https://www.jira-net.or.jp/publishing/files/jesra/JESRA_TR-0042_2018.pdf)「5.1 レポート種別コード」に記載されているLOINCコード [Diagnostic imaging study](https://loinc.org/18748-4/) を指定。コードを指定できない場合はCodeableConceptを使用せずテキスト等を直接コーディングすることも許容されるが、要素間の調整と事前・事後の内容の整合性確保のために独自の構造を提供する必要があるので留意すること。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1083,7 +1083,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Group|4.0.1|Device|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Group|Device|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
 </t>
   </si>
   <si>
@@ -1119,7 +1119,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -1225,7 +1225,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner)
 </t>
   </si>
   <si>
@@ -1278,7 +1278,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
@@ -1306,7 +1306,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Radiology_Findings|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Radiology_Impression|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Radiology_Findings|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Radiology_Impression|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common)
 </t>
   </si>
   <si>
@@ -1332,7 +1332,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ImagingStudy_Radiology|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ImagingStudy_Radiology)
 </t>
   </si>
   <si>
@@ -1421,7 +1421,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media|4.0.1)
+    <t xml:space="preserve">Reference(Media)
 </t>
   </si>
   <si>
@@ -1481,7 +1481,7 @@
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
@@ -1839,7 +1839,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="214.1484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="190.17578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1854,7 +1854,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="62.875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
